--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,122 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133872025</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106262</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602523</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654944</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106262</v>
+        <v>106266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106266</v>
+        <v>106268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106268</v>
+        <v>106296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106296</v>
+        <v>106306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106306</v>
+        <v>106307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106307</v>
+        <v>106309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>133872025</v>
       </c>
       <c r="B4" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>112683200</v>
       </c>
       <c r="B2" t="n">
-        <v>91222</v>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,66 +784,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120432197</v>
+        <v>69681402</v>
       </c>
       <c r="B3" t="n">
-        <v>105145</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängshäll, 680 m O om, Upl</t>
+          <t>Runhällen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602635</v>
+        <v>602642</v>
       </c>
       <c r="R3" t="n">
-        <v>6654955</v>
+        <v>6654544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,17 +848,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Enåker</t>
+          <t>Västerlövsta</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,81 +867,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Hedbarrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Sundberg</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Sundberg</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133872025</v>
+        <v>15018855</v>
       </c>
       <c r="B4" t="n">
-        <v>106317</v>
+        <v>12237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåfläckig kvickbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Anthicus bimaculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Illiger, 1801)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fallfälla</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Runhällen, Upl</t>
+          <t>Ingbo, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602523</v>
+        <v>602478</v>
       </c>
       <c r="R4" t="n">
-        <v>6654944</v>
+        <v>6654895</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2008-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:59</t>
+          <t>2008-08-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>OrigNr 8Metod: fallfönsterfälla</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,18 +981,599 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grustäkt</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Gunnar Sjödin</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120432197</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ängshäll, 680 m O om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602635</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6654955</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hedbarrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133872025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602523</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6654944</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Beke Regelin</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Beke Regelin</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74098532</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ängshäll, 790 m O om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>602738</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6654989</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-11-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-11-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en yta av ca 5 x 10 m. Såg ut som karakteristisk plattlummer med breda, gulgröna och glesa skott i våningar och med mest 2 långa sporax per stjälk.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Hedtallskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ca 70-årig åstallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg, Mora Aronsson, Kerstin Frostberg, Karin Wiklund, Karin Haulin, Anders Helander, Ola Löfgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133872024</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602845</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6654901</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133872026</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602617</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6654861</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21717-2026 artfynd.xlsx
+++ b/artfynd/A 21717-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112683200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15018855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432197</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74098532</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1574,8 +1614,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>